--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486676_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486676_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4877</v>
+        <v>9.3583</v>
       </c>
       <c r="E2" t="n">
-        <v>9.800599999999999</v>
+        <v>8.8698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6872</v>
+        <v>0.4885</v>
       </c>
       <c r="G2" t="n">
         <v>6.7856</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4398</v>
+        <v>0.3104</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2959</v>
+        <v>0.3651</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1439</v>
+        <v>-0.0547</v>
       </c>
       <c r="V2" t="n">
         <v>2.4554</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.6907</v>
+        <v>7.306</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8548</v>
+        <v>5.5446</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8359</v>
+        <v>1.7614</v>
       </c>
       <c r="G3" t="n">
         <v>3.6787</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2744</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6339</v>
+        <v>0.3237</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6404</v>
+        <v>0.5659</v>
       </c>
       <c r="V3" t="n">
         <v>0.6138</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3481</v>
+        <v>4.8611</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7065</v>
+        <v>3.1201</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6417</v>
+        <v>1.741</v>
       </c>
       <c r="G4" t="n">
         <v>2.9064</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4577</v>
+        <v>0.0553</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>-0.1106</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1659</v>
       </c>
       <c r="V4" t="n">
         <v>1.5133</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7231</v>
+        <v>4.1783</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0961</v>
+        <v>3.3029</v>
       </c>
       <c r="F5" t="n">
-        <v>0.627</v>
+        <v>0.8753</v>
       </c>
       <c r="G5" t="n">
         <v>3.3094</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1655</v>
+        <v>0.2896</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1932</v>
+        <v>0.0136</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0277</v>
+        <v>0.276</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9246</v>
+        <v>2.5729</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6487</v>
+        <v>2.5453</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2759</v>
+        <v>0.0276</v>
       </c>
       <c r="G6" t="n">
         <v>0.369</v>
@@ -922,13 +922,13 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7174</v>
+        <v>0.3656</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1865</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8004</v>
+        <v>0.5521</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8334</v>
+        <v>1.7654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7302</v>
+        <v>-0.093</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1033</v>
+        <v>1.8584</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4544</v>
+        <v>2.0342</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1379</v>
+        <v>1.7381</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3165</v>
+        <v>0.2961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0407</v>
+        <v>1.3938</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.3938</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4137</v>
+        <v>0.6404</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1379</v>
+        <v>0.3443</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2758</v>
+        <v>0.2961</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7226</v>
+        <v>0.6966</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6895</v>
+        <v>0.1584</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0331</v>
+        <v>0.5382</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2759</v>
+        <v>1.582</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7901</v>
+        <v>1.997</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5143</v>
+        <v>-0.4149</v>
       </c>
       <c r="G8" t="n">
         <v>1.9408</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5957</v>
+        <v>-0.2896</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0279</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1738</v>
+        <v>1.4694</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6101</v>
+        <v>0.3165</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7839</v>
+        <v>1.1529</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0342</v>
+        <v>0.4544</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7381</v>
+        <v>0.1379</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2961</v>
+        <v>0.3165</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3938</v>
+        <v>0.0407</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3938</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6404</v>
+        <v>0.4137</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3443</v>
+        <v>0.1379</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2961</v>
+        <v>0.2758</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.105</v>
+        <v>0.3586</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3587</v>
+        <v>0.2758</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4637</v>
+        <v>0.0828</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.202</v>
+        <v>-0.0489</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6488</v>
+        <v>-0.5454</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4468</v>
+        <v>0.4965</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2351</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0331</v>
+        <v>0.1862</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8053</v>
+        <v>-2.2489</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1523</v>
+        <v>-0.5168</v>
       </c>
       <c r="F11" t="n">
-        <v>1.347</v>
+        <v>-1.7321</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3845</v>
+        <v>-1.5245</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1648</v>
+        <v>-1.1583</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5493</v>
+        <v>-0.3662</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6268</v>
+        <v>-0.5304</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0265</v>
+        <v>-0.5372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6534</v>
+        <v>0.0069</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2423</v>
+        <v>-0.9942</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1382</v>
+        <v>-0.6211</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1041</v>
+        <v>-0.3731</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.2823</v>
+        <v>0.9654</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0925</v>
+        <v>0.1517</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0825</v>
+        <v>0.0135</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>0.1382</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1178</v>
+        <v>-2.4632</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1374</v>
+        <v>-3.4625</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9804</v>
+        <v>0.9993</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5245</v>
+        <v>0.3845</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1583</v>
+        <v>-0.1648</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3662</v>
+        <v>0.5493</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5304</v>
+        <v>0.6268</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5372</v>
+        <v>-0.0265</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0069</v>
+        <v>0.6534</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9942</v>
+        <v>-0.2423</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6211</v>
+        <v>-0.1382</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3731</v>
+        <v>-0.1041</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9654</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7171</v>
+        <v>0.4346</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.607</v>
+        <v>-0.2278</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1101</v>
+        <v>0.6624</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>28.33220000000001</v>
+        <v>28.3324</v>
       </c>
       <c r="E13" t="n">
-        <v>21.0784</v>
+        <v>21.0785</v>
       </c>
       <c r="F13" t="n">
-        <v>7.254</v>
+        <v>7.2539</v>
       </c>
       <c r="G13" t="n">
         <v>20.1034</v>
@@ -1447,7 +1447,7 @@
         <v>20.00660000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.5897</v>
+        <v>4.589700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-4.4929</v>
@@ -1468,13 +1468,13 @@
         <v>12.5501</v>
       </c>
       <c r="S13" t="n">
-        <v>3.448800000000001</v>
+        <v>3.4486</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4112000000000002</v>
+        <v>0.4112</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0374</v>
+        <v>3.0375</v>
       </c>
       <c r="V13" t="n">
         <v>1.8842</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.466</v>
+        <v>1.0039</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4122</v>
+        <v>3.8259</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9462</v>
+        <v>-2.822</v>
       </c>
       <c r="G14" t="n">
         <v>0.7634</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.324</v>
+        <v>-0.7861</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9933</v>
+        <v>-0.5796</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3307</v>
+        <v>-0.2065</v>
       </c>
       <c r="V14" t="n">
         <v>1.7989</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0974</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0805</v>
+        <v>0.1839</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0169</v>
+        <v>-0.0936</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6928</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0827</v>
+        <v>-0.0897</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4693</v>
+        <v>-0.3659</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3866</v>
+        <v>0.2762</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2533</v>
+        <v>-0.2284</v>
       </c>
       <c r="E16" t="n">
         <v>-0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0732</v>
+        <v>-0.0484</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2974</v>
@@ -1702,13 +1702,13 @@
         <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3421</v>
+        <v>-0.3172</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1213</v>
+        <v>-0.0965</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7397</v>
+        <v>-0.6156</v>
       </c>
       <c r="E17" t="n">
         <v>-0.2497</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.49</v>
+        <v>-0.3659</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4362</v>
@@ -1780,13 +1780,13 @@
         <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6897</v>
+        <v>-0.5655</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4966</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7974</v>
+        <v>-1.6884</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7085</v>
+        <v>-0.8119</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0889</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6608000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0219</v>
+        <v>0.1309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0498</v>
+        <v>0.2622</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2757</v>
+        <v>-3.7154</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2437</v>
+        <v>0.0027</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5194</v>
+        <v>-3.7181</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5633</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>1.743</v>
+        <v>0.3033</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4614</v>
+        <v>0.2204</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2816</v>
+        <v>0.083</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2277</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8089</v>
+        <v>-3.9384</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.962</v>
+        <v>-2.1625</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8469</v>
+        <v>-1.7759</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8243</v>
+        <v>-0.9631</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3246</v>
+        <v>-0.6828</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4996</v>
+        <v>-0.2803</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6187</v>
+        <v>0.1271</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3316</v>
+        <v>0.2831</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2871</v>
+        <v>-0.1559</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.443</v>
+        <v>-1.0903</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.6562</v>
+        <v>-0.9659</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1244</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5446</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0892</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.502</v>
+        <v>-0.1105</v>
       </c>
       <c r="T20" t="n">
-        <v>0.165</v>
+        <v>-0.3589</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3371</v>
+        <v>0.2484</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9421</v>
+        <v>-1.5133</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3907</v>
+        <v>-4.5454</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5762</v>
+        <v>-1.3757</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8145</v>
+        <v>-3.1697</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9631</v>
+        <v>-1.8243</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6828</v>
+        <v>-1.3246</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2803</v>
+        <v>-0.4996</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1271</v>
+        <v>2.6187</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2831</v>
+        <v>2.3316</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1559</v>
+        <v>0.2871</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0903</v>
+        <v>-4.443</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9659</v>
+        <v>-3.6562</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1244</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3515</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-3.0892</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5627</v>
+        <v>-0.2345</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.2487</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2098</v>
+        <v>0.0143</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5133</v>
+        <v>-0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5133</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1049</v>
+        <v>-6.6112</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1074</v>
+        <v>-1.9005</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9975</v>
+        <v>-4.7107</v>
       </c>
       <c r="G22" t="n">
         <v>-6.4593</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8386</v>
+        <v>-0.3449</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5245</v>
+        <v>-0.3177</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3141</v>
+        <v>-0.0272</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.5251</v>
+        <v>-7.3942</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2065</v>
+        <v>-4.586</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3186</v>
+        <v>-2.8082</v>
       </c>
       <c r="G23" t="n">
         <v>-5.9695</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8758</v>
+        <v>-0.7449</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1588</v>
+        <v>-0.5383</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.717</v>
+        <v>-0.2066</v>
       </c>
       <c r="V23" t="n">
         <v>0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-28.3323</v>
+        <v>-27.6427</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2539</v>
+        <v>-7.2538</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.0783</v>
+        <v>-20.389</v>
       </c>
       <c r="G24" t="n">
         <v>-20.1033</v>
@@ -2326,13 +2326,13 @@
         <v>9.6538</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.4487</v>
+        <v>-2.7591</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.0372</v>
+        <v>-3.0373</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4112000000000001</v>
+        <v>0.2784</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8842</v>
